--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. VIC - UNIVERSITAT DE VIC.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. VIC - UNIVERSITAT DE VIC.xlsx
@@ -565,13 +565,13 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>79.6069</v>
+        <v>60.7005</v>
       </c>
       <c r="E2" t="n">
-        <v>64.105</v>
+        <v>48.1675</v>
       </c>
       <c r="F2" t="n">
-        <v>15.5021</v>
+        <v>12.5335</v>
       </c>
       <c r="G2" t="n">
         <v>22.7465</v>
@@ -610,13 +610,13 @@
         <v>39.8503</v>
       </c>
       <c r="S2" t="n">
-        <v>46.6985</v>
+        <v>27.7922</v>
       </c>
       <c r="T2" t="n">
-        <v>33.4053</v>
+        <v>17.4673</v>
       </c>
       <c r="U2" t="n">
-        <v>13.2933</v>
+        <v>10.3247</v>
       </c>
       <c r="V2" t="n">
         <v>22.4685</v>
@@ -643,13 +643,13 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>74.3015</v>
+        <v>54.0221</v>
       </c>
       <c r="E3" t="n">
-        <v>43.2326</v>
+        <v>26.7278</v>
       </c>
       <c r="F3" t="n">
-        <v>31.0691</v>
+        <v>27.2944</v>
       </c>
       <c r="G3" t="n">
         <v>16.5899</v>
@@ -688,13 +688,13 @@
         <v>46.8821</v>
       </c>
       <c r="S3" t="n">
-        <v>41.7794</v>
+        <v>21.5001</v>
       </c>
       <c r="T3" t="n">
-        <v>30.6178</v>
+        <v>14.1132</v>
       </c>
       <c r="U3" t="n">
-        <v>11.1614</v>
+        <v>7.387</v>
       </c>
       <c r="V3" t="n">
         <v>5.1885</v>
@@ -721,13 +721,13 @@
         <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>19.6363</v>
+        <v>27.4979</v>
       </c>
       <c r="E4" t="n">
-        <v>8.489100000000001</v>
+        <v>12.7543</v>
       </c>
       <c r="F4" t="n">
-        <v>11.1473</v>
+        <v>14.7439</v>
       </c>
       <c r="G4" t="n">
         <v>15.3241</v>
@@ -766,13 +766,13 @@
         <v>38.0917</v>
       </c>
       <c r="S4" t="n">
-        <v>4.6546</v>
+        <v>12.5161</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8436</v>
+        <v>6.109</v>
       </c>
       <c r="U4" t="n">
-        <v>2.8105</v>
+        <v>6.4071</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1467000000000003</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>P. MARTINEZ ALEJANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>18.938</v>
+        <v>19.5903</v>
       </c>
       <c r="E5" t="n">
-        <v>22.5858</v>
+        <v>19.9122</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.647699999999999</v>
+        <v>-0.3218999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5919</v>
+        <v>11.4795</v>
       </c>
       <c r="H5" t="n">
-        <v>21.5321</v>
+        <v>7.5926</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.9405</v>
+        <v>3.8871</v>
       </c>
       <c r="J5" t="n">
-        <v>24.7729</v>
+        <v>20.219</v>
       </c>
       <c r="K5" t="n">
-        <v>22.9379</v>
+        <v>12.5491</v>
       </c>
       <c r="L5" t="n">
-        <v>1.835</v>
+        <v>7.6698</v>
       </c>
       <c r="M5" t="n">
-        <v>-10.1807</v>
+        <v>-8.7393</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4056</v>
+        <v>-4.9566</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.7753</v>
+        <v>-3.7826</v>
       </c>
       <c r="P5" t="n">
-        <v>-11.33</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q5" t="n">
-        <v>-30.0828</v>
+        <v>-15.6275</v>
       </c>
       <c r="R5" t="n">
-        <v>18.7527</v>
+        <v>12.3067</v>
       </c>
       <c r="S5" t="n">
-        <v>19.7888</v>
+        <v>4.6723</v>
       </c>
       <c r="T5" t="n">
-        <v>19.0851</v>
+        <v>3.1314</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7035000000000002</v>
+        <v>1.541</v>
       </c>
       <c r="V5" t="n">
-        <v>-4.113</v>
+        <v>6.758900000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>8.8104</v>
+        <v>12.1892</v>
       </c>
       <c r="X5" t="n">
-        <v>-12.9233</v>
+        <v>-5.430199999999999</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>12.3678</v>
+        <v>19.3666</v>
       </c>
       <c r="E6" t="n">
-        <v>9.807700000000001</v>
+        <v>15.1248</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5602</v>
+        <v>4.2418</v>
       </c>
       <c r="G6" t="n">
         <v>17.696</v>
@@ -922,13 +922,13 @@
         <v>26.1758</v>
       </c>
       <c r="S6" t="n">
-        <v>-5.5324</v>
+        <v>1.4665</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.7403</v>
+        <v>1.5766</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.792</v>
+        <v>-0.1104000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>-4.8744</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MARTINEZ ALEJANO</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>10.5513</v>
+        <v>14.626</v>
       </c>
       <c r="E7" t="n">
-        <v>13.0371</v>
+        <v>0.6508000000000012</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4859</v>
+        <v>13.9752</v>
       </c>
       <c r="G7" t="n">
-        <v>11.4795</v>
+        <v>28.1258</v>
       </c>
       <c r="H7" t="n">
-        <v>7.5926</v>
+        <v>33.1214</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8871</v>
+        <v>-4.995</v>
       </c>
       <c r="J7" t="n">
-        <v>20.219</v>
+        <v>54.0745</v>
       </c>
       <c r="K7" t="n">
-        <v>12.5491</v>
+        <v>44.0812</v>
       </c>
       <c r="L7" t="n">
-        <v>7.6698</v>
+        <v>9.992999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-8.7393</v>
+        <v>-25.9479</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.9566</v>
+        <v>-10.9601</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.7826</v>
+        <v>-14.9882</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.3208</v>
+        <v>-27.7386</v>
       </c>
       <c r="Q7" t="n">
-        <v>-15.6275</v>
+        <v>-79.50450000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>12.3067</v>
+        <v>51.7661</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.3666</v>
+        <v>19.7319</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.7435</v>
+        <v>11.0494</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.623</v>
+        <v>8.681699999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>6.758900000000001</v>
+        <v>-5.4929</v>
       </c>
       <c r="W7" t="n">
-        <v>12.1892</v>
+        <v>15.0313</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.430199999999999</v>
+        <v>-20.5246</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>9.947099999999999</v>
+        <v>11.6388</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.501500000000001</v>
+        <v>5.202199999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>12.4487</v>
+        <v>6.4367</v>
       </c>
       <c r="G8" t="n">
-        <v>28.1258</v>
+        <v>-12.6965</v>
       </c>
       <c r="H8" t="n">
-        <v>33.1214</v>
+        <v>-6.733000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.995</v>
+        <v>-5.9634</v>
       </c>
       <c r="J8" t="n">
-        <v>54.0745</v>
+        <v>4.843800000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>44.0812</v>
+        <v>6.3479</v>
       </c>
       <c r="L8" t="n">
-        <v>9.992999999999999</v>
+        <v>-1.504</v>
       </c>
       <c r="M8" t="n">
-        <v>-25.9479</v>
+        <v>-17.5402</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.9601</v>
+        <v>-13.0809</v>
       </c>
       <c r="O8" t="n">
-        <v>-14.9882</v>
+        <v>-4.4593</v>
       </c>
       <c r="P8" t="n">
-        <v>-27.7386</v>
+        <v>6.4463</v>
       </c>
       <c r="Q8" t="n">
-        <v>-79.50450000000001</v>
+        <v>-17.5806</v>
       </c>
       <c r="R8" t="n">
-        <v>51.7661</v>
+        <v>24.027</v>
       </c>
       <c r="S8" t="n">
-        <v>15.0526</v>
+        <v>0.00969999999999982</v>
       </c>
       <c r="T8" t="n">
-        <v>7.897200000000001</v>
+        <v>-0.7851</v>
       </c>
       <c r="U8" t="n">
-        <v>7.1555</v>
+        <v>0.7950999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-5.4929</v>
+        <v>17.8793</v>
       </c>
       <c r="W8" t="n">
-        <v>15.0313</v>
+        <v>18.7243</v>
       </c>
       <c r="X8" t="n">
-        <v>-20.5246</v>
+        <v>-0.8447999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. SABATÉS SALA</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>7.946199999999999</v>
+        <v>10.7898</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8058</v>
+        <v>0.1385000000000003</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1404</v>
+        <v>10.6514</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9246</v>
+        <v>-0.180499999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3544</v>
+        <v>-5.360099999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4297</v>
+        <v>5.180099999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4517</v>
+        <v>16.0535</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2604</v>
+        <v>5.331199999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1913</v>
+        <v>10.7224</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.527</v>
+        <v>-16.2337</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9060999999999999</v>
+        <v>-10.6911</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6209</v>
+        <v>-5.5425</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1254</v>
+        <v>13.088</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.0788</v>
+        <v>-21.0969</v>
       </c>
       <c r="R9" t="n">
-        <v>8.2044</v>
+        <v>34.185</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2511</v>
+        <v>3.5446</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.9998</v>
+        <v>1.4133</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7488</v>
+        <v>2.1313</v>
       </c>
       <c r="V9" t="n">
-        <v>3.147</v>
+        <v>-5.6623</v>
       </c>
       <c r="W9" t="n">
-        <v>4.4327</v>
+        <v>3.7683</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2856</v>
+        <v>-9.4308</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>4.421099999999999</v>
+        <v>10.0918</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2084000000000005</v>
+        <v>12.555</v>
       </c>
       <c r="F10" t="n">
-        <v>4.212999999999999</v>
+        <v>-2.462899999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-12.6965</v>
+        <v>14.5919</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.733000000000001</v>
+        <v>21.5321</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.9634</v>
+        <v>-6.9405</v>
       </c>
       <c r="J10" t="n">
-        <v>4.843800000000001</v>
+        <v>24.7729</v>
       </c>
       <c r="K10" t="n">
-        <v>6.3479</v>
+        <v>22.9379</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.504</v>
+        <v>1.835</v>
       </c>
       <c r="M10" t="n">
-        <v>-17.5402</v>
+        <v>-10.1807</v>
       </c>
       <c r="N10" t="n">
-        <v>-13.0809</v>
+        <v>-1.4056</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.4593</v>
+        <v>-8.7753</v>
       </c>
       <c r="P10" t="n">
-        <v>6.4463</v>
+        <v>-11.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>-17.5806</v>
+        <v>-30.0828</v>
       </c>
       <c r="R10" t="n">
-        <v>24.027</v>
+        <v>18.7527</v>
       </c>
       <c r="S10" t="n">
-        <v>-7.2078</v>
+        <v>10.9426</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.779</v>
+        <v>9.0541</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4289</v>
+        <v>1.8886</v>
       </c>
       <c r="V10" t="n">
-        <v>17.8793</v>
+        <v>-4.113</v>
       </c>
       <c r="W10" t="n">
-        <v>18.7243</v>
+        <v>8.8104</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8447999999999999</v>
+        <v>-12.9233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>È. ARUMÍ COLOM</t>
+          <t>G. SABATÉS SALA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5816</v>
+        <v>9.049299999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0392</v>
+        <v>3.0996</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6207</v>
+        <v>5.949800000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8209</v>
+        <v>1.9246</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1468</v>
+        <v>2.3544</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6741</v>
+        <v>-0.4297</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0819</v>
+        <v>4.4517</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0819</v>
+        <v>3.2604</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.1913</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7391</v>
+        <v>-2.527</v>
       </c>
       <c r="N11" t="n">
-        <v>0.065</v>
+        <v>-0.9060999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6741</v>
+        <v>-1.6209</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>3.1254</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-5.0788</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>8.2044</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4347</v>
+        <v>0.8521000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.121</v>
+        <v>-0.7058</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3137</v>
+        <v>1.5581</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>3.147</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>4.4327</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2856</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2803999999999995</v>
+        <v>3.2026</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9833</v>
+        <v>4.178199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.703200000000001</v>
+        <v>-0.975200000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.6597</v>
+        <v>10.0349</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.6663</v>
+        <v>-5.741300000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9935</v>
+        <v>15.7763</v>
       </c>
       <c r="J12" t="n">
-        <v>5.069</v>
+        <v>20.0207</v>
       </c>
       <c r="K12" t="n">
-        <v>5.4361</v>
+        <v>1.8071</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3671000000000002</v>
+        <v>18.2136</v>
       </c>
       <c r="M12" t="n">
-        <v>-11.7285</v>
+        <v>-9.985799999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-10.1021</v>
+        <v>-7.5482</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6263</v>
+        <v>-2.4375</v>
       </c>
       <c r="P12" t="n">
-        <v>7.0322</v>
+        <v>7.0323</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.6273</v>
+        <v>-21.2922</v>
       </c>
       <c r="R12" t="n">
-        <v>22.6598</v>
+        <v>28.3247</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2684</v>
+        <v>3.1435</v>
       </c>
       <c r="T12" t="n">
-        <v>4.7313</v>
+        <v>2.013</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.463</v>
+        <v>1.1301</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3607</v>
+        <v>-17.0078</v>
       </c>
       <c r="W12" t="n">
-        <v>8.8104</v>
+        <v>3.4363</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.1711</v>
+        <v>-20.4441</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1539999999999999</v>
+        <v>3.125</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4564</v>
+        <v>3.305899999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6104</v>
+        <v>-0.1808999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7990999999999997</v>
+        <v>-6.6597</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2026</v>
+        <v>-4.6663</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4035</v>
+        <v>-1.9935</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1244999999999999</v>
+        <v>5.069</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2801999999999998</v>
+        <v>5.4361</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4046</v>
+        <v>-0.3671000000000002</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9237000000000001</v>
+        <v>-11.7285</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9225</v>
+        <v>-10.1021</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.001299999999999968</v>
+        <v>-1.6263</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3907</v>
+        <v>7.0322</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.8835</v>
+        <v>-15.6273</v>
       </c>
       <c r="R13" t="n">
-        <v>4.492999999999999</v>
+        <v>22.6598</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7263</v>
+        <v>4.1128</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6897</v>
+        <v>5.053900000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0366</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.3824</v>
+        <v>-1.3607</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.387</v>
+        <v>8.8104</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.9954</v>
+        <v>-10.1711</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. PALLARES ARUMI</t>
+          <t>È. ARUMÍ COLOM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1348</v>
+        <v>0.92</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.163</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1348</v>
+        <v>0.7569</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1348</v>
+        <v>0.8209</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.1468</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1348</v>
+        <v>0.6741</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.0819</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.0819</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1348</v>
+        <v>0.7391</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1348</v>
+        <v>0.6741</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0.0963</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-0.1775</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.06120000000000037</v>
+        <v>0.3260000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.485200000000001</v>
+        <v>-2.230100000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>7.423900000000001</v>
+        <v>2.5561</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.180499999999999</v>
+        <v>-8.3971</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.360099999999999</v>
+        <v>-4.2587</v>
       </c>
       <c r="I15" t="n">
-        <v>5.180099999999999</v>
+        <v>-4.1384</v>
       </c>
       <c r="J15" t="n">
-        <v>16.0535</v>
+        <v>4.8403</v>
       </c>
       <c r="K15" t="n">
-        <v>5.331199999999999</v>
+        <v>3.1732</v>
       </c>
       <c r="L15" t="n">
-        <v>10.7224</v>
+        <v>1.6669</v>
       </c>
       <c r="M15" t="n">
-        <v>-16.2337</v>
+        <v>-13.2375</v>
       </c>
       <c r="N15" t="n">
-        <v>-10.6911</v>
+        <v>-7.432</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.5425</v>
+        <v>-5.805499999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>13.088</v>
+        <v>4.1022</v>
       </c>
       <c r="Q15" t="n">
-        <v>-21.0969</v>
+        <v>-15.0412</v>
       </c>
       <c r="R15" t="n">
-        <v>34.185</v>
+        <v>19.1435</v>
       </c>
       <c r="S15" t="n">
-        <v>-7.3064</v>
+        <v>0.4359</v>
       </c>
       <c r="T15" t="n">
-        <v>-6.21</v>
+        <v>0.7689</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0961</v>
+        <v>-0.3328</v>
       </c>
       <c r="V15" t="n">
-        <v>-5.6623</v>
+        <v>4.1848</v>
       </c>
       <c r="W15" t="n">
-        <v>3.7683</v>
+        <v>7.201899999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.4308</v>
+        <v>-3.0171</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>P. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2678</v>
+        <v>0.1348</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.4118</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.144</v>
+        <v>0.1348</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.3971</v>
+        <v>0.1348</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.2587</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.1384</v>
+        <v>0.1348</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8403</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1732</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6669</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-13.2375</v>
+        <v>0.1348</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.432</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.805499999999999</v>
+        <v>0.1348</v>
       </c>
       <c r="P16" t="n">
-        <v>4.1022</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-15.0412</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>19.1435</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1577</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5872000000000002</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.745</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.1848</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>7.201899999999999</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.0171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8054</v>
+        <v>-1.4222</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7044</v>
+        <v>-0.2394000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1011</v>
+        <v>-1.1828</v>
       </c>
       <c r="G17" t="n">
         <v>-1.3819</v>
@@ -1780,13 +1780,13 @@
         <v>0.3906</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1271</v>
+        <v>0.5103</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4237</v>
+        <v>0.0413</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5508</v>
+        <v>0.4691</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9413999999999999</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SOY BASSOLS</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.038</v>
+        <v>-1.8836</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0794</v>
+        <v>-4.6499</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9584999999999999</v>
+        <v>2.7663</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7468</v>
+        <v>-0.7990999999999997</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0164</v>
+        <v>-1.2026</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2696</v>
+        <v>0.4035</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3277</v>
+        <v>0.1244999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3277</v>
+        <v>-0.2801999999999998</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.4046</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.419</v>
+        <v>-0.9237000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6886</v>
+        <v>-0.9225</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2696</v>
+        <v>-0.001299999999999968</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5627</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-4.8835</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>4.492999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8260000000000001</v>
+        <v>1.6885</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9245</v>
+        <v>0.4962</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0985</v>
+        <v>1.1924</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5543999999999999</v>
+        <v>-2.3824</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>-0.387</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8317</v>
+        <v>-1.9954</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.1278</v>
+        <v>-2.5487</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2521</v>
+        <v>-12.0698</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.875599999999999</v>
+        <v>9.5212</v>
       </c>
       <c r="G19" t="n">
-        <v>10.0349</v>
+        <v>10.2328</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.741300000000001</v>
+        <v>-2.474</v>
       </c>
       <c r="I19" t="n">
-        <v>15.7763</v>
+        <v>12.7061</v>
       </c>
       <c r="J19" t="n">
-        <v>20.0207</v>
+        <v>26.4894</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8071</v>
+        <v>11.073</v>
       </c>
       <c r="L19" t="n">
-        <v>18.2136</v>
+        <v>15.4165</v>
       </c>
       <c r="M19" t="n">
-        <v>-9.985799999999999</v>
+        <v>-16.2566</v>
       </c>
       <c r="N19" t="n">
-        <v>-7.5482</v>
+        <v>-13.5467</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.4375</v>
+        <v>-2.7102</v>
       </c>
       <c r="P19" t="n">
-        <v>7.0323</v>
+        <v>-4.2976</v>
       </c>
       <c r="Q19" t="n">
-        <v>-21.2922</v>
+        <v>-42.5844</v>
       </c>
       <c r="R19" t="n">
-        <v>28.3247</v>
+        <v>38.2874</v>
       </c>
       <c r="S19" t="n">
-        <v>-6.1874</v>
+        <v>1.2892</v>
       </c>
       <c r="T19" t="n">
-        <v>-4.4172</v>
+        <v>0.6986999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.7704</v>
+        <v>0.5903</v>
       </c>
       <c r="V19" t="n">
-        <v>-17.0078</v>
+        <v>-9.7729</v>
       </c>
       <c r="W19" t="n">
-        <v>3.4363</v>
+        <v>3.3265</v>
       </c>
       <c r="X19" t="n">
-        <v>-20.4441</v>
+        <v>-13.0995</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>M. SOY BASSOLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>-17.3695</v>
+        <v>-3.5902</v>
       </c>
       <c r="E20" t="n">
-        <v>-22.7863</v>
+        <v>-2.6861</v>
       </c>
       <c r="F20" t="n">
-        <v>5.4168</v>
+        <v>-0.9040999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>10.2328</v>
+        <v>-1.7468</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.474</v>
+        <v>-2.0164</v>
       </c>
       <c r="I20" t="n">
-        <v>12.7061</v>
+        <v>0.2696</v>
       </c>
       <c r="J20" t="n">
-        <v>26.4894</v>
+        <v>-1.3277</v>
       </c>
       <c r="K20" t="n">
-        <v>11.073</v>
+        <v>-1.3277</v>
       </c>
       <c r="L20" t="n">
-        <v>15.4165</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-16.2566</v>
+        <v>-0.419</v>
       </c>
       <c r="N20" t="n">
-        <v>-13.5467</v>
+        <v>-0.6886</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.7102</v>
+        <v>0.2696</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.2976</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q20" t="n">
-        <v>-42.5844</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>38.2874</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>-13.5319</v>
+        <v>0.2738</v>
       </c>
       <c r="T20" t="n">
-        <v>-10.0179</v>
+        <v>0.3179</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.5138</v>
+        <v>-0.044</v>
       </c>
       <c r="V20" t="n">
-        <v>-9.7729</v>
+        <v>-0.5543999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>3.3265</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>-13.0995</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="21">
@@ -2047,19 +2047,19 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>209.1973</v>
+        <v>235.6368</v>
       </c>
       <c r="E21" t="n">
-        <v>122.5385</v>
+        <v>130.1045</v>
       </c>
       <c r="F21" t="n">
-        <v>86.65939999999998</v>
+        <v>105.5342</v>
       </c>
       <c r="G21" t="n">
         <v>117.8401</v>
       </c>
       <c r="H21" t="n">
-        <v>72.63810000000001</v>
+        <v>72.63809999999998</v>
       </c>
       <c r="I21" t="n">
         <v>45.2028</v>
@@ -2083,25 +2083,25 @@
         <v>-70.2817</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.907399999999999</v>
+        <v>-3.907399999999998</v>
       </c>
       <c r="Q21" t="n">
-        <v>-418.0315</v>
+        <v>-418.0315000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>414.1268</v>
+        <v>414.1267999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>87.94570000000002</v>
+        <v>114.3858</v>
       </c>
       <c r="T21" t="n">
-        <v>64.3293</v>
+        <v>71.89449999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>23.616</v>
+        <v>42.4908</v>
       </c>
       <c r="V21" t="n">
-        <v>7.318099999999998</v>
+        <v>7.318100000000002</v>
       </c>
       <c r="W21" t="n">
         <v>165.8517</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. VIC - UNIVERSITAT DE VIC.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. VIC - UNIVERSITAT DE VIC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. SABATÉS SALA</t>
+          <t>G. SABATES SALA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,28 +1267,28 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>9.049299999999999</v>
+        <v>8.128299999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0996</v>
+        <v>2.1786</v>
       </c>
       <c r="F11" t="n">
         <v>5.949800000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9246</v>
+        <v>1.0037</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3544</v>
+        <v>1.4334</v>
       </c>
       <c r="I11" t="n">
         <v>-0.4297</v>
       </c>
       <c r="J11" t="n">
-        <v>4.4517</v>
+        <v>3.5307</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2604</v>
+        <v>2.3395</v>
       </c>
       <c r="L11" t="n">
         <v>1.1913</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>3.2026</v>
+        <v>4.884</v>
       </c>
       <c r="E12" t="n">
-        <v>4.178199999999999</v>
+        <v>4.884</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.975200000000001</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>10.0349</v>
+        <v>4.884</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.741300000000001</v>
+        <v>2.456</v>
       </c>
       <c r="I12" t="n">
-        <v>15.7763</v>
+        <v>2.428</v>
       </c>
       <c r="J12" t="n">
-        <v>20.0207</v>
+        <v>4.884</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8071</v>
+        <v>2.456</v>
       </c>
       <c r="L12" t="n">
-        <v>18.2136</v>
+        <v>2.428</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.985799999999999</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.5482</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.4375</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>7.0323</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-21.2922</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>28.3247</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1435</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.013</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1301</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>-17.0078</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.4363</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-20.4441</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>3.125</v>
+        <v>3.2026</v>
       </c>
       <c r="E13" t="n">
-        <v>3.305899999999999</v>
+        <v>4.178199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1808999999999999</v>
+        <v>-0.975200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.6597</v>
+        <v>10.0349</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.6663</v>
+        <v>-5.741300000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.9935</v>
+        <v>15.7763</v>
       </c>
       <c r="J13" t="n">
-        <v>5.069</v>
+        <v>20.0207</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4361</v>
+        <v>1.8071</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3671000000000002</v>
+        <v>18.2136</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.7285</v>
+        <v>-9.985799999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.1021</v>
+        <v>-7.5482</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.6263</v>
+        <v>-2.4375</v>
       </c>
       <c r="P13" t="n">
-        <v>7.0322</v>
+        <v>7.0323</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.6273</v>
+        <v>-21.2922</v>
       </c>
       <c r="R13" t="n">
-        <v>22.6598</v>
+        <v>28.3247</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1128</v>
+        <v>3.1435</v>
       </c>
       <c r="T13" t="n">
-        <v>5.053900000000001</v>
+        <v>2.013</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9409999999999999</v>
+        <v>1.1301</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.3607</v>
+        <v>-17.0078</v>
       </c>
       <c r="W13" t="n">
-        <v>8.8104</v>
+        <v>3.4363</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.1711</v>
+        <v>-20.4441</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>È. ARUMÍ COLOM</t>
+          <t>G. SABATÉS SALA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,61 +1498,61 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="E14" t="n">
-        <v>0.163</v>
+        <v>0.921</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7569</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8209</v>
+        <v>0.921</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1468</v>
+        <v>0.921</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6741</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0819</v>
+        <v>0.921</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0819</v>
+        <v>0.921</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7391</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6741</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0963</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.08119999999999999</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1775</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>E. ARUMI COLOM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3260000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.230100000000001</v>
+        <v>0.163</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5561</v>
+        <v>0.7569</v>
       </c>
       <c r="G15" t="n">
-        <v>-8.3971</v>
+        <v>0.8209</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.2587</v>
+        <v>0.1468</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.1384</v>
+        <v>0.6741</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8403</v>
+        <v>0.0819</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1732</v>
+        <v>0.0819</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6669</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-13.2375</v>
+        <v>0.7391</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.432</v>
+        <v>0.065</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.805499999999999</v>
+        <v>0.6741</v>
       </c>
       <c r="P15" t="n">
-        <v>4.1022</v>
+        <v>0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-15.0412</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>19.1435</v>
+        <v>0.1953</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4359</v>
+        <v>-0.0963</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7689</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3328</v>
+        <v>-0.1775</v>
       </c>
       <c r="V15" t="n">
-        <v>4.1848</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>7.201899999999999</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.0171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. PALLARES ARUMI</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1348</v>
+        <v>0.3260000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-2.230100000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1348</v>
+        <v>2.5561</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1348</v>
+        <v>-8.3971</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-4.2587</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1348</v>
+        <v>-4.1384</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>4.8403</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3.1732</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.6669</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1348</v>
+        <v>-13.2375</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-7.432</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1348</v>
+        <v>-5.805499999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.1022</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-15.0412</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>19.1435</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.4359</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.7689</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.3328</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.1848</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>7.201899999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-3.0171</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CARRERA PRAT</t>
+          <t>P. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4222</v>
+        <v>0.1348</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2394000000000001</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1828</v>
+        <v>0.1348</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3819</v>
+        <v>0.1348</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9908000000000001</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.391</v>
+        <v>0.1348</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5579999999999999</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1024</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6602000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8238999999999999</v>
+        <v>0.1348</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0931</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2692</v>
+        <v>0.1348</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3906</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3906</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5103</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0413</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4691</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9413999999999999</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>J. CARRERA PRAT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8836</v>
+        <v>-1.4222</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.6499</v>
+        <v>-0.2394000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7663</v>
+        <v>-1.1828</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7990999999999997</v>
+        <v>-1.3819</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2026</v>
+        <v>-0.9908000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4035</v>
+        <v>-0.391</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1244999999999999</v>
+        <v>-0.5579999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2801999999999998</v>
+        <v>0.1024</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4046</v>
+        <v>-0.6602000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9237000000000001</v>
+        <v>-0.8238999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9225</v>
+        <v>-1.0931</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.001299999999999968</v>
+        <v>0.2692</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>0.3906</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.8835</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.492999999999999</v>
+        <v>0.3906</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6885</v>
+        <v>0.5103</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4962</v>
+        <v>0.0413</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1924</v>
+        <v>0.4691</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.3824</v>
+        <v>-0.9413999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.387</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.9954</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5487</v>
+        <v>-1.759</v>
       </c>
       <c r="E19" t="n">
-        <v>-12.0698</v>
+        <v>-1.578</v>
       </c>
       <c r="F19" t="n">
-        <v>9.5212</v>
+        <v>-0.1808999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>10.2328</v>
+        <v>-11.5435</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.474</v>
+        <v>-7.1222</v>
       </c>
       <c r="I19" t="n">
-        <v>12.7061</v>
+        <v>-4.4215</v>
       </c>
       <c r="J19" t="n">
-        <v>26.4894</v>
+        <v>0.1851</v>
       </c>
       <c r="K19" t="n">
-        <v>11.073</v>
+        <v>2.9801</v>
       </c>
       <c r="L19" t="n">
-        <v>15.4165</v>
+        <v>-2.7951</v>
       </c>
       <c r="M19" t="n">
-        <v>-16.2566</v>
+        <v>-11.7285</v>
       </c>
       <c r="N19" t="n">
-        <v>-13.5467</v>
+        <v>-10.1021</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.7102</v>
+        <v>-1.6263</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.2976</v>
+        <v>7.0322</v>
       </c>
       <c r="Q19" t="n">
-        <v>-42.5844</v>
+        <v>-15.6273</v>
       </c>
       <c r="R19" t="n">
-        <v>38.2874</v>
+        <v>22.6598</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2892</v>
+        <v>4.1128</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6986999999999999</v>
+        <v>5.053900000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5903</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-9.7729</v>
+        <v>-1.3607</v>
       </c>
       <c r="W19" t="n">
-        <v>3.3265</v>
+        <v>8.8104</v>
       </c>
       <c r="X19" t="n">
-        <v>-13.0995</v>
+        <v>-10.1711</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SOY BASSOLS</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5902</v>
+        <v>-1.8836</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6861</v>
+        <v>-4.6499</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9040999999999999</v>
+        <v>2.7663</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7468</v>
+        <v>-0.7990999999999997</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0164</v>
+        <v>-1.2026</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2696</v>
+        <v>0.4035</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3277</v>
+        <v>0.1244999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3277</v>
+        <v>-0.2801999999999998</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.4046</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.419</v>
+        <v>-0.9237000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6886</v>
+        <v>-0.9225</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2696</v>
+        <v>-0.001299999999999968</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5627</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-4.8835</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3907</v>
+        <v>4.492999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2738</v>
+        <v>1.6885</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3179</v>
+        <v>0.4962</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.044</v>
+        <v>1.1924</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5543999999999999</v>
+        <v>-2.3824</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>-0.387</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8317</v>
+        <v>-1.9954</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,66 +2047,222 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
+        <v>-2.5487</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-12.0698</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9.5212</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10.2328</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-2.474</v>
+      </c>
+      <c r="I21" t="n">
+        <v>12.7061</v>
+      </c>
+      <c r="J21" t="n">
+        <v>26.4894</v>
+      </c>
+      <c r="K21" t="n">
+        <v>11.073</v>
+      </c>
+      <c r="L21" t="n">
+        <v>15.4165</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-16.2566</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-13.5467</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-2.7102</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-4.2976</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-42.5844</v>
+      </c>
+      <c r="R21" t="n">
+        <v>38.2874</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.2892</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.6986999999999999</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.5903</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-9.7729</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.3265</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-13.0995</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>M. SOY BASSOLS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-3.5902</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-2.6861</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.9040999999999999</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.7468</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-2.0164</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1.3277</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-1.3277</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.419</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.6886</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.2738</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.5543999999999999</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.8317</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>26</v>
+      </c>
+      <c r="D23" t="n">
         <v>235.6368</v>
       </c>
-      <c r="E21" t="n">
-        <v>130.1045</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="E23" t="n">
+        <v>130.1046</v>
+      </c>
+      <c r="F23" t="n">
         <v>105.5342</v>
       </c>
-      <c r="G21" t="n">
-        <v>117.8401</v>
-      </c>
-      <c r="H21" t="n">
-        <v>72.63809999999998</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="G23" t="n">
+        <v>117.8404</v>
+      </c>
+      <c r="H23" t="n">
+        <v>72.63819999999997</v>
+      </c>
+      <c r="I23" t="n">
         <v>45.2028</v>
       </c>
-      <c r="J21" t="n">
-        <v>310.3887</v>
-      </c>
-      <c r="K21" t="n">
-        <v>194.9041</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="J23" t="n">
+        <v>310.3888</v>
+      </c>
+      <c r="K23" t="n">
+        <v>194.9042</v>
+      </c>
+      <c r="L23" t="n">
         <v>115.4836</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M23" t="n">
         <v>-192.5461</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N23" t="n">
         <v>-122.266</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O23" t="n">
         <v>-70.2817</v>
       </c>
-      <c r="P21" t="n">
-        <v>-3.907399999999998</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-418.0315000000001</v>
-      </c>
-      <c r="R21" t="n">
-        <v>414.1267999999999</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="P23" t="n">
+        <v>-3.907399999999997</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-418.0315</v>
+      </c>
+      <c r="R23" t="n">
+        <v>414.1268</v>
+      </c>
+      <c r="S23" t="n">
         <v>114.3858</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T23" t="n">
         <v>71.89449999999999</v>
       </c>
-      <c r="U21" t="n">
-        <v>42.4908</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7.318100000000002</v>
-      </c>
-      <c r="W21" t="n">
+      <c r="U23" t="n">
+        <v>42.49079999999999</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.318099999999998</v>
+      </c>
+      <c r="W23" t="n">
         <v>165.8517</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X23" t="n">
         <v>-158.5353</v>
       </c>
     </row>
